--- a/ฟอร์ม.xlsx
+++ b/ฟอร์ม.xlsx
@@ -567,7 +567,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2063074" cy="2030152"/>
+    <xdr:ext cx="857250" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
